--- a/xls/square_16_quad4_15.xlsx
+++ b/xls/square_16_quad4_15.xlsx
@@ -456,6 +456,76 @@
         <v>10</v>
       </c>
     </row>
+    <row r="13" spans="1:11">
+      <c r="A13" t="s">
+        <v>11</v>
+      </c>
+      <c r="B13">
+        <v>256</v>
+      </c>
+      <c r="C13" t="s">
+        <v>11</v>
+      </c>
+      <c r="D13">
+        <v>289</v>
+      </c>
+      <c r="E13" t="s">
+        <v>12</v>
+      </c>
+      <c r="F13">
+        <v>196</v>
+      </c>
+      <c r="G13" t="s">
+        <v>13</v>
+      </c>
+      <c r="H13">
+        <v>507</v>
+      </c>
+      <c r="I13">
+        <v>2.3996583667120057</v>
+      </c>
+      <c r="J13">
+        <v>0.05928117943828821</v>
+      </c>
+      <c r="K13">
+        <v>0.7144984422830816</v>
+      </c>
+    </row>
+    <row r="14" spans="1:11">
+      <c r="A14" t="s">
+        <v>11</v>
+      </c>
+      <c r="B14">
+        <v>256</v>
+      </c>
+      <c r="C14" t="s">
+        <v>11</v>
+      </c>
+      <c r="D14">
+        <v>289</v>
+      </c>
+      <c r="E14" t="s">
+        <v>12</v>
+      </c>
+      <c r="F14">
+        <v>225</v>
+      </c>
+      <c r="G14" t="s">
+        <v>13</v>
+      </c>
+      <c r="H14">
+        <v>588</v>
+      </c>
+      <c r="I14">
+        <v>0.8953109003272989</v>
+      </c>
+      <c r="J14">
+        <v>-0.597677513398173</v>
+      </c>
+      <c r="K14">
+        <v>0.08154359006686665</v>
+      </c>
+    </row>
     <row r="15" spans="1:11">
       <c r="A15" t="s">
         <v>11</v>
@@ -482,13 +552,13 @@
         <v>675</v>
       </c>
       <c r="I15">
-        <v>0.5058717815304087</v>
+        <v>-0.44104787877819257</v>
       </c>
       <c r="J15">
-        <v>-1.7035327346891922</v>
+        <v>-1.4016399120117813</v>
       </c>
       <c r="K15">
-        <v>-0.9799670491245399</v>
+        <v>-1.1093841387304906</v>
       </c>
     </row>
     <row r="16" spans="1:11">
@@ -517,13 +587,13 @@
         <v>768</v>
       </c>
       <c r="I16">
-        <v>-1.7860120231328833</v>
+        <v>-1.4464158825552127</v>
       </c>
       <c r="J16">
-        <v>-1.7974679224507608</v>
+        <v>-1.501301608256671</v>
       </c>
       <c r="K16">
-        <v>-1.4243348908642486</v>
+        <v>-1.367878873061532</v>
       </c>
     </row>
     <row r="17" spans="1:11">
@@ -552,13 +622,13 @@
         <v>867</v>
       </c>
       <c r="I17">
-        <v>-1.8289654952321748</v>
+        <v>-1.4819824558907857</v>
       </c>
       <c r="J17">
-        <v>-1.8419218629899352</v>
+        <v>-1.5215549128563008</v>
       </c>
       <c r="K17">
-        <v>-0.810322203584669</v>
+        <v>0.535475751880026</v>
       </c>
     </row>
     <row r="18" spans="1:11">
@@ -587,13 +657,13 @@
         <v>972</v>
       </c>
       <c r="I18">
-        <v>-1.8090166011109368</v>
+        <v>-1.5277678608397456</v>
       </c>
       <c r="J18">
-        <v>-1.8139692012444957</v>
+        <v>-1.6035470073851867</v>
       </c>
       <c r="K18">
-        <v>1.4120701336911146</v>
+        <v>1.6612831902333338</v>
       </c>
     </row>
     <row r="19" spans="1:11">
@@ -622,13 +692,13 @@
         <v>1083</v>
       </c>
       <c r="I19">
-        <v>-1.7880037289144466</v>
+        <v>-1.5562129814733887</v>
       </c>
       <c r="J19">
-        <v>-1.788780353153674</v>
+        <v>-1.6214604734838334</v>
       </c>
       <c r="K19">
-        <v>1.758339143194205</v>
+        <v>3.149893847921515</v>
       </c>
     </row>
     <row r="20" spans="1:11">
@@ -657,13 +727,13 @@
         <v>1200</v>
       </c>
       <c r="I20">
-        <v>-1.6825623138659627</v>
+        <v>-0.9029874591211575</v>
       </c>
       <c r="J20">
-        <v>-1.365500712313597</v>
+        <v>-0.7532094527147549</v>
       </c>
       <c r="K20">
-        <v>3.113324551618283</v>
+        <v>4.756351889038313</v>
       </c>
     </row>
     <row r="21" spans="1:11">
@@ -692,13 +762,13 @@
         <v>1323</v>
       </c>
       <c r="I21">
-        <v>-0.6251823689788634</v>
+        <v>-0.06154694628027247</v>
       </c>
       <c r="J21">
-        <v>-0.4020842858458142</v>
+        <v>-0.0553808940872794</v>
       </c>
       <c r="K21">
-        <v>3.6525559816023057</v>
+        <v>4.679843899896379</v>
       </c>
     </row>
     <row r="22" spans="1:11">
@@ -727,13 +797,13 @@
         <v>1452</v>
       </c>
       <c r="I22">
-        <v>-0.12999426336978326</v>
+        <v>-0.0025001932739172708</v>
       </c>
       <c r="J22">
-        <v>-0.12386958893207024</v>
+        <v>-0.002281222468594471</v>
       </c>
       <c r="K22">
-        <v>3.870085113773571</v>
+        <v>4.0644686967759585</v>
       </c>
     </row>
     <row r="23" spans="1:11">
@@ -762,13 +832,13 @@
         <v>1587</v>
       </c>
       <c r="I23">
-        <v>-0.00999646229849089</v>
+        <v>-0.00015307131974773354</v>
       </c>
       <c r="J23">
-        <v>-0.007522474506201189</v>
+        <v>-0.00012001233112517256</v>
       </c>
       <c r="K23">
-        <v>3.318980756937244</v>
+        <v>3.3996657901538034</v>
       </c>
     </row>
     <row r="24" spans="1:11">
@@ -797,13 +867,13 @@
         <v>1728</v>
       </c>
       <c r="I24">
-        <v>-0.008746055669504421</v>
+        <v>-9.860241189827414e-5</v>
       </c>
       <c r="J24">
-        <v>-0.007319829330973597</v>
+        <v>-8.147657680404118e-5</v>
       </c>
       <c r="K24">
-        <v>3.34659744739079</v>
+        <v>3.3428473737382296</v>
       </c>
     </row>
     <row r="25" spans="1:11">
@@ -832,13 +902,13 @@
         <v>1875</v>
       </c>
       <c r="I25">
-        <v>-0.002195320370873108</v>
+        <v>-2.333028809560293e-5</v>
       </c>
       <c r="J25">
-        <v>-0.0020163531003668687</v>
+        <v>-2.1162654852845674e-5</v>
       </c>
       <c r="K25">
-        <v>3.0918326654924564</v>
+        <v>3.0753639152505734</v>
       </c>
     </row>
     <row r="26" spans="1:11">
@@ -867,13 +937,13 @@
         <v>2028</v>
       </c>
       <c r="I26">
-        <v>-0.0009576931658007622</v>
+        <v>-8.84092486589752e-6</v>
       </c>
       <c r="J26">
-        <v>-0.0008284905244584972</v>
+        <v>-7.774985033617238e-6</v>
       </c>
       <c r="K26">
-        <v>2.890333928391497</v>
+        <v>2.846237622736692</v>
       </c>
     </row>
     <row r="27" spans="1:11">
@@ -902,13 +972,13 @@
         <v>2187</v>
       </c>
       <c r="I27">
-        <v>-0.0012601578630702024</v>
+        <v>-1.0315566803237927e-5</v>
       </c>
       <c r="J27">
-        <v>-0.0010635105688654855</v>
+        <v>-8.719737628731806e-6</v>
       </c>
       <c r="K27">
-        <v>2.9429628890683217</v>
+        <v>2.8646522565357784</v>
       </c>
     </row>
     <row r="28" spans="1:11">
@@ -937,13 +1007,13 @@
         <v>2352</v>
       </c>
       <c r="I28">
-        <v>-0.0007260319826595735</v>
+        <v>-5.90934037723755e-6</v>
       </c>
       <c r="J28">
-        <v>-0.0007066299950586421</v>
+        <v>-5.7681937906170896e-6</v>
       </c>
       <c r="K28">
-        <v>2.87493817185302</v>
+        <v>2.796869227872407</v>
       </c>
     </row>
     <row r="29" spans="1:11">
@@ -972,13 +1042,13 @@
         <v>2523</v>
       </c>
       <c r="I29">
-        <v>4.557302525761023e-6</v>
+        <v>3.222173638408736e-8</v>
       </c>
       <c r="J29">
-        <v>3.537500868360094e-7</v>
+        <v>-5.141438148827934e-9</v>
       </c>
       <c r="K29">
-        <v>1.791864259429722</v>
+        <v>1.7757057988240683</v>
       </c>
     </row>
     <row r="30" spans="1:11">
@@ -1007,13 +1077,13 @@
         <v>2700</v>
       </c>
       <c r="I30">
-        <v>-9.149650102807961e-6</v>
+        <v>-1.0653626540916409e-7</v>
       </c>
       <c r="J30">
-        <v>-7.44992684925635e-6</v>
+        <v>-9.276386977389738e-8</v>
       </c>
       <c r="K30">
-        <v>1.824143986336163</v>
+        <v>1.8564139635623211</v>
       </c>
     </row>
     <row r="31" spans="1:11">
@@ -1042,13 +1112,13 @@
         <v>2883</v>
       </c>
       <c r="I31">
-        <v>-6.267171161071907e-7</v>
+        <v>-9.83624166926609e-9</v>
       </c>
       <c r="J31">
-        <v>-7.099716209463882e-7</v>
+        <v>-1.0907183470308033e-8</v>
       </c>
       <c r="K31">
-        <v>1.4132277618270455</v>
+        <v>1.460559365856568</v>
       </c>
     </row>
     <row r="32" spans="1:11">
@@ -1077,13 +1147,13 @@
         <v>3072</v>
       </c>
       <c r="I32">
-        <v>-2.0090191981174946e-6</v>
+        <v>-2.7276089892827056e-8</v>
       </c>
       <c r="J32">
-        <v>-1.6362285561684606e-6</v>
+        <v>-2.2634743438670252e-8</v>
       </c>
       <c r="K32">
-        <v>1.4904772010833165</v>
+        <v>1.5366345691314125</v>
       </c>
     </row>
   </sheetData>
